--- a/outputs/evaluation/decision/v2/CF_M08/run_2/CF_M08_decision_eval_gt_report.xlsx
+++ b/outputs/evaluation/decision/v2/CF_M08/run_2/CF_M08_decision_eval_gt_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,23 +471,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CF_M08_AD02</t>
+          <t>CF_M08_AD03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Traefik opens port 80 to handle non-secure HTTP traffic re-
-directing this traffic to port 443 (HTTPS) to ensure that all communications are carried out safely.</t>
+          <t>HTTPS encrypts the data transmitted between the clients and the server, protecting the integrity and confidentiality of the information.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>*CF_M08_C10</t>
+          <t>*CF_M08_C11, *CF_M08_C12</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CF_M08_AU03</t>
+          <t>CF_M08_AU22</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -495,12 +494,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Responsiveness</t>
+          <t>Security; Integrity</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Traefik</t>
+          <t>Docker</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -510,11 +509,11 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>HTTPS encrypts the data transmitted between the clients and the server, protecting the integrity and confidentiality of the information.</t>
+          <t>Traefik opens port 443 to handle HTTPS traffic, which is the standard for secure communications on the web. HTTPS encrypts the data transmitted between clients and the server, protecting the integrity and confidentiality of the information.</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.757</v>
+        <v>0.8749</v>
       </c>
     </row>
     <row r="3">
@@ -553,16 +552,16 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>AD_05</t>
+          <t>AD_04</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>This approach promotes modularity, code reuse, and maintainability, facilitating the management of the application.</t>
+          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components. This approach promotes modularity, the reuse of code and maintainability, facilitating the management of the application.</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.6589</v>
+        <v>0.584</v>
       </c>
     </row>
     <row r="4">
@@ -606,11 +605,11 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Next.js is a framework for building web applications that offers additional structure, features, and optimizations that allow building applications faster and without the need to configure tools manually.</t>
+          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components. This approach promotes modularity, the reuse of code and maintainability, facilitating the management of the application.</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.7467</v>
+        <v>0.5822000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -649,16 +648,16 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>AD_04</t>
+          <t>AD_02</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Next.js is a framework for building web applications that offers additional structure, features, and optimizations that allow building applications faster and without the need to configure tools manually.</t>
+          <t>Traefik acts as a reverse proxy and load balancer, distributing traffic between multiple instances of a service, improving the availability and responsiveness of the application.</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.7212</v>
+        <v>0.6473</v>
       </c>
     </row>
     <row r="6">
@@ -697,16 +696,16 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>AD_05</t>
+          <t>AD_04</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>This approach promotes modularity, code reuse, and maintainability, facilitating the management of the application.</t>
+          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components. This approach promotes modularity, the reuse of code and maintainability, facilitating the management of the application.</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0.7174</v>
+        <v>0.7005</v>
       </c>
     </row>
     <row r="7">
@@ -735,7 +734,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Efficiency (of development); Flexibility</t>
+          <t>Efficiency; Flexibility</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -750,11 +749,11 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Next.js is a framework for building web applications that offers additional structure, features, and optimizations that allow building applications faster and without the need to configure tools manually.</t>
+          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components. This approach promotes modularity, the reuse of code and maintainability, facilitating the management of the application.</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0.6631</v>
+        <v>0.6881</v>
       </c>
     </row>
     <row r="8">
@@ -798,11 +797,11 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Next.js is a framework for building web applications that offers additional structure, features, and optimizations that allow building applications faster and without the need to configure tools manually.</t>
+          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components. This approach promotes modularity, the reuse of code and maintainability, facilitating the management of the application.</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0.7241</v>
+        <v>0.7336</v>
       </c>
     </row>
     <row r="9">
@@ -841,16 +840,16 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>AD_05</t>
+          <t>AD_07</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>This approach promotes modularity, code reuse, and maintainability, facilitating the management of the application.</t>
+          <t>Prisma is an ORM tool used to simplify database access and management.</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>0.7407</v>
+        <v>0.7812</v>
       </c>
     </row>
     <row r="10">
@@ -894,59 +893,11 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Docker is used to create an application and package it together with its dependencies and libraries in a container, allowing to develop locally, raise a database, and build an image that can be deployed in different environments.</t>
+          <t>Prisma is an ORM tool used to simplify database access and management.</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>0.5719</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>CF_M08_AD12</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Prisma Studio is a visual tool to explore and edit data in the database. It provides a graphical interface to visualize and manipulate the data, facilitating development and debugging.</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>*CF_M08_C24</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>CF_M08_AU09</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>50</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Depuration</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Prisma</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>AD_07</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Docker is used to create an application and package it together with its dependencies and libraries in a container, allowing to develop locally, raise a database, and build an image that can be deployed in different environments.</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>0.5989</v>
+        <v>0.7723</v>
       </c>
     </row>
   </sheetData>
